--- a/laderr-rules-0.4.0.xlsx
+++ b/laderr-rules-0.4.0.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FavatoBarcelosPP\Dev\laderr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531B4C7C-A8A4-4068-A63D-FB7FC83F88A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9444C349-199E-4F04-A9B7-737C94F4EC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{89084A5C-62F7-4402-9527-9AFD86D07F17}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{89084A5C-62F7-4402-9527-9AFD86D07F17}"/>
   </bookViews>
   <sheets>
-    <sheet name="LaDeRR Rules" sheetId="1" r:id="rId1"/>
-    <sheet name="Implementation" sheetId="2" r:id="rId2"/>
+    <sheet name="Metamodel" sheetId="1" r:id="rId1"/>
+    <sheet name="Metamodel - Classification" sheetId="6" r:id="rId2"/>
+    <sheet name="Implementation" sheetId="2" r:id="rId3"/>
+    <sheet name="Implementation - Query" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
   <si>
     <t>ID</t>
   </si>
@@ -396,6 +398,122 @@
   </si>
   <si>
     <t>For any LaderrSpecification, its scenario is classified as incident if and only if the scenario is either resilient or not_resilient, but not both.</t>
+  </si>
+  <si>
+    <t>rule_endangers</t>
+  </si>
+  <si>
+    <t>rule_damaged1</t>
+  </si>
+  <si>
+    <t>rule_damaged2</t>
+  </si>
+  <si>
+    <t>rule_damaged3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">\forall o1, o2 ( Entity(o1) \land Entity(o2) \land ( \exists ls, d2 ( LaderrSpecification(ls) \land Capability(d2) \land composedOf(ls, o1) \land composedOf(ls, o2) \land threatens(o2, o1) \land capabilities(o1, d2) \land scenario(ls) = NOT_RESILIENT \land \neg \exists r ( Resilience(r) \land preserves(r, d2) ) ) ) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\rightarrow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> damaged(o2, o1) )</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">\forall o1, o2 ( Entity(o1) \land Entity(o2) \land ( \exists ls, d2 ( LaderrSpecification(ls) \land Capability(d2) \land composedOf(ls, o1) \land composedOf(ls, o2) \land threatens(o2, o1) \land capabilities(o1, d2) \land scenario(ls) = OPERATIONAL \land \neg \exists r ( Resilience(r) \land preserves(r, d2) ) ) ) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\rightarrow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> endangers(o2, o1) ) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">\forall o1, o2 ( Entity(o1) \land Entity(o2) \land ( \exists ls, d2 ( LaderrSpecification(ls) \land Capability(d2) \land composedOf(ls, o1) \land composedOf(ls, o2) \land threatens(o2, o1) \land capabilities(o1, d2) \land scenario(ls) = INCIDENT \land \neg \exists r ( Resilience(r) \land preserves(r, d2) ) ) ) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">\rightarrow </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(damaged(o2, o1) \land \text{next}scenario(ls) = NOT_RESILIENT) ) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">\forall o1, o2 ( Entity(o1) \land Entity(o2) \land ( \exists ls ( LaderrSpecification(ls) \land composedOf(ls, o1) \land composedOf(ls, o2) \land damaged(o2, o1) \land scenario(ls) = INCIDENT ) ) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\rightarrow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> \text{\(next\)}scenario(ls) = NOT_RESILIENT )</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -486,10 +604,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -498,11 +613,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="24">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -544,36 +662,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -609,19 +697,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -651,17 +726,80 @@
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -677,25 +815,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DDAA19EC-8B06-4B50-9281-3B528691A616}" name="Table2" displayName="Table2" ref="A1:D10" totalsRowShown="0" dataDxfId="11">
-  <autoFilter ref="A1:D10" xr:uid="{6A61511C-102D-4762-9C27-47AA11DC235F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DDAA19EC-8B06-4B50-9281-3B528691A616}" name="Table2" displayName="Table2" ref="A1:D9" totalsRowShown="0" dataDxfId="23">
+  <autoFilter ref="A1:D9" xr:uid="{6A61511C-102D-4762-9C27-47AA11DC235F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6D44803A-FA6F-4387-8AE2-D6904BF340C0}" name="ID" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{77DF9B09-EE73-435F-A33E-2409873D9CB5}" name="Type" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{DC1C6A68-12DE-4142-8148-6524BAFF4555}" name="Description" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{B06AC0DE-69E3-46CD-A38E-29859BCF0AF7}" name="Rule" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{6D44803A-FA6F-4387-8AE2-D6904BF340C0}" name="ID" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{77DF9B09-EE73-435F-A33E-2409873D9CB5}" name="Type" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{DC1C6A68-12DE-4142-8148-6524BAFF4555}" name="Description" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{B06AC0DE-69E3-46CD-A38E-29859BCF0AF7}" name="Rule" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EC57CC3-8775-470D-BF25-2976FBA37329}" name="Table23" displayName="Table23" ref="A1:C5" totalsRowShown="0" headerRowDxfId="18" dataDxfId="13">
-  <autoFilter ref="A1:C5" xr:uid="{3EC57CC3-8775-470D-BF25-2976FBA37329}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B42D1344-8725-48F8-957F-E5C83D920FDD}" name="Table25" displayName="Table25" ref="A1:D2" totalsRowShown="0" dataDxfId="8">
+  <autoFilter ref="A1:D2" xr:uid="{6A61511C-102D-4762-9C27-47AA11DC235F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{D5AB007C-DB2C-46F7-903D-D4BA2CFC812B}" name="ID" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{66D0C608-C4B7-4D49-B1ED-9992DA2A49CE}" name="Type" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{EDD43604-6EE5-4E36-93B5-30A7862D2CCF}" name="Description" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{9E33B5F8-115B-44F0-8305-33C2E63AEA68}" name="Rule" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EC57CC3-8775-470D-BF25-2976FBA37329}" name="Table23" displayName="Table23" ref="A1:C9" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:C9" xr:uid="{3EC57CC3-8775-470D-BF25-2976FBA37329}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{7583DACA-EA4E-4F15-A3CE-26B92A7CEDCD}" name="ID" dataDxfId="16"/>
     <tableColumn id="3" xr3:uid="{008D278D-04CC-4C24-B634-B5F450BB2DA5}" name="Type" dataDxfId="15"/>
     <tableColumn id="7" xr3:uid="{21EC58EF-8D6C-4DA1-A4E2-612F16715A40}" name="Rule" dataDxfId="14"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0E2AFD4E-30D4-4730-A8B0-1E3F3E885DFE}" name="Table234" displayName="Table234" ref="A1:C9" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:C9" xr:uid="{3EC57CC3-8775-470D-BF25-2976FBA37329}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{C92D44FB-A4E2-4AE2-B673-41DD5963DAA4}" name="ID" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{1A1F2BC5-A7C6-418E-A5DF-B00FFF0F7CA9}" name="Type" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{E1B65664-5172-4AAC-B407-996BA4F71691}" name="Rule" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1021,7 +1184,7 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -1115,67 +1278,53 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>37</v>
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>25</v>
+      <c r="A8" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>33</v>
+      <c r="A9" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D999">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="A2:A998">
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A999">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  <conditionalFormatting sqref="D2:D998">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1186,11 +1335,68 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A76A81-36BF-489D-86FE-F109877CC0B8}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="185.42578125" customWidth="1"/>
+    <col min="4" max="4" width="135.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:A991">
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D991">
+    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D946266-0A86-4978-80E4-B4AFAA127E85}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -1210,7 +1416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,7 +1427,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1232,7 +1438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1243,7 +1449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1253,6 +1459,120 @@
       <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
+    </row>
+    <row r="6" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9DEF13-5832-44D1-A6BA-FA4E55F08B69}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="188.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
